--- a/vgjewellry/public/sample/quotation_template.xlsx
+++ b/vgjewellry/public/sample/quotation_template.xlsx
@@ -130,6 +130,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -151,11 +152,13 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -205,11 +208,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -499,12 +502,12 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C1:C1002" type="list">
-      <formula1>"Bangles,Button,Cufflink,Pendant,Polki,Ring,Set,Tops"</formula1>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F1:F1002" type="list">
+      <formula1>"Gold 14KT,Gold 18KT,Platinum"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F1:F1002" type="list">
-      <formula1>"Gold 14KT,Gold 18KT,Platinum"</formula1>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C1:C1002" type="list">
+      <formula1>"Bangles,Button,Cufflink,Pendant,Polki,Ring,Set,Tops,Chain,Bali,Tanmania,Mangalsutra"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
